--- a/assets/Absensi.xlsx
+++ b/assets/Absensi.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Download\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Only Personal Project\Random Projek\AbsenItc2\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F483DE1E-778C-454B-8192-8F182F15AE8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51B5EFDD-5050-4BCB-BC2D-0E9A3EB6C950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="5" xr2:uid="{F37292F1-6F59-4E90-B5FC-8EE81FE23FFE}"/>
   </bookViews>
@@ -769,7 +769,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -819,11 +819,21 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="15" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -844,19 +854,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="15" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1187,31 +1184,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.649999999999999" customHeight="1">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1">
       <c r="A4" s="13"/>
@@ -1248,10 +1245,10 @@
       <c r="C7" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="D7" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="E7" s="25"/>
+      <c r="E7" s="29"/>
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1">
       <c r="A8" s="4">
@@ -2511,10 +2508,10 @@
       <c r="B75" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="D75" s="26" t="s">
+      <c r="D75" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="E75" s="26"/>
+      <c r="E75" s="30"/>
     </row>
     <row r="76" spans="1:5" ht="15.5">
       <c r="B76" s="15" t="s">
@@ -2554,10 +2551,10 @@
       <c r="B83" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="D83" s="21" t="s">
+      <c r="D83" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="E83" s="21"/>
+      <c r="E83" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -2588,31 +2585,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.649999999999999" customHeight="1">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1">
       <c r="A4" s="13"/>
@@ -2649,10 +2646,10 @@
       <c r="C7" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="D7" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="E7" s="25"/>
+      <c r="E7" s="29"/>
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1">
       <c r="A8" s="4">
@@ -3912,10 +3909,10 @@
       <c r="B75" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="D75" s="26" t="s">
+      <c r="D75" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="E75" s="26"/>
+      <c r="E75" s="30"/>
     </row>
     <row r="76" spans="1:5" ht="15.5">
       <c r="B76" s="15" t="s">
@@ -3955,10 +3952,10 @@
       <c r="B83" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="D83" s="21" t="s">
+      <c r="D83" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="E83" s="21"/>
+      <c r="E83" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -3989,31 +3986,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.649999999999999" customHeight="1">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1">
       <c r="A4" s="13"/>
@@ -4050,10 +4047,10 @@
       <c r="C7" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="D7" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="E7" s="25"/>
+      <c r="E7" s="29"/>
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1">
       <c r="A8" s="4">
@@ -5313,10 +5310,10 @@
       <c r="B75" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="D75" s="26" t="s">
+      <c r="D75" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="E75" s="26"/>
+      <c r="E75" s="30"/>
     </row>
     <row r="76" spans="1:5" ht="15.5">
       <c r="B76" s="15" t="s">
@@ -5356,10 +5353,10 @@
       <c r="B83" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="D83" s="21" t="s">
+      <c r="D83" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="E83" s="21"/>
+      <c r="E83" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -5390,31 +5387,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.649999999999999" customHeight="1">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1">
       <c r="A4" s="13"/>
@@ -5451,10 +5448,10 @@
       <c r="C7" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="D7" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="E7" s="25"/>
+      <c r="E7" s="29"/>
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1">
       <c r="A8" s="4">
@@ -6714,10 +6711,10 @@
       <c r="B75" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="D75" s="26" t="s">
+      <c r="D75" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="E75" s="26"/>
+      <c r="E75" s="30"/>
     </row>
     <row r="76" spans="1:5" ht="15.5">
       <c r="B76" s="15" t="s">
@@ -6757,10 +6754,10 @@
       <c r="B83" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="D83" s="21" t="s">
+      <c r="D83" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="E83" s="21"/>
+      <c r="E83" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -6791,31 +6788,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.649999999999999" customHeight="1">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1">
       <c r="A4" s="13"/>
@@ -6852,10 +6849,10 @@
       <c r="C7" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="D7" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="E7" s="25"/>
+      <c r="E7" s="29"/>
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1">
       <c r="A8" s="4">
@@ -8115,10 +8112,10 @@
       <c r="B75" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="D75" s="26" t="s">
+      <c r="D75" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="E75" s="26"/>
+      <c r="E75" s="30"/>
     </row>
     <row r="76" spans="1:5" ht="15.5">
       <c r="B76" s="15" t="s">
@@ -8158,10 +8155,10 @@
       <c r="B83" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="D83" s="21" t="s">
+      <c r="D83" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="E83" s="21"/>
+      <c r="E83" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -8192,31 +8189,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.649999999999999" customHeight="1">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="31" t="s">
         <v>99</v>
       </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1">
       <c r="A4" s="13"/>
@@ -8244,7 +8241,7 @@
       <c r="E6" s="14"/>
     </row>
     <row r="7" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="17" t="s">
         <v>96</v>
       </c>
       <c r="B7" s="17" t="s">
@@ -8253,10 +8250,10 @@
       <c r="C7" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="D7" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="E7" s="25"/>
+      <c r="E7" s="29"/>
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1">
       <c r="A8" s="18">
@@ -8268,11 +8265,11 @@
       <c r="C8" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="28">
-        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
+      <c r="D8" s="20">
+        <f t="shared" ref="D8:D50" si="0">IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
         <v>1</v>
       </c>
-      <c r="E8" s="29"/>
+      <c r="E8" s="21"/>
     </row>
     <row r="9" spans="1:5" ht="15.75" customHeight="1">
       <c r="A9" s="18">
@@ -8284,12 +8281,12 @@
       <c r="C9" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D9" s="28" t="str">
-        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
-        <v/>
-      </c>
-      <c r="E9" s="29">
-        <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
+      <c r="D9" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E9" s="21">
+        <f t="shared" ref="E9:E50" si="1">IF(ISODD(ROW()-7),"",ROW()-7)</f>
         <v>2</v>
       </c>
     </row>
@@ -8303,12 +8300,12 @@
       <c r="C10" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="28">
-        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
-        <v>3</v>
-      </c>
-      <c r="E10" s="29" t="str">
-        <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
+      <c r="D10" s="20">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="E10" s="21" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -8322,12 +8319,12 @@
       <c r="C11" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D11" s="28" t="str">
-        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
-        <v/>
-      </c>
-      <c r="E11" s="29">
-        <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
+      <c r="D11" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E11" s="21">
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
@@ -8341,12 +8338,12 @@
       <c r="C12" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="28">
-        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
+      <c r="D12" s="20">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="E12" s="29" t="str">
-        <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
+      <c r="E12" s="21" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -8360,12 +8357,12 @@
       <c r="C13" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D13" s="28" t="str">
-        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
-        <v/>
-      </c>
-      <c r="E13" s="29">
-        <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
+      <c r="D13" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E13" s="21">
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
     </row>
@@ -8379,12 +8376,12 @@
       <c r="C14" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="28">
-        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
+      <c r="D14" s="20">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="E14" s="29" t="str">
-        <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
+      <c r="E14" s="21" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -8398,12 +8395,12 @@
       <c r="C15" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="28" t="str">
-        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
-        <v/>
-      </c>
-      <c r="E15" s="29">
-        <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
+      <c r="D15" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E15" s="21">
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
     </row>
@@ -8411,18 +8408,18 @@
       <c r="A16" s="18">
         <v>9</v>
       </c>
-      <c r="B16" s="30" t="s">
+      <c r="B16" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="C16" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="D16" s="28">
-        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
+      <c r="C16" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="20">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="E16" s="29" t="str">
-        <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
+      <c r="E16" s="21" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -8436,12 +8433,12 @@
       <c r="C17" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D17" s="28" t="str">
-        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
-        <v/>
-      </c>
-      <c r="E17" s="29">
-        <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
+      <c r="D17" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E17" s="21">
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
@@ -8455,12 +8452,12 @@
       <c r="C18" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="28">
-        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
+      <c r="D18" s="20">
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="E18" s="29" t="str">
-        <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
+      <c r="E18" s="21" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -8474,12 +8471,12 @@
       <c r="C19" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D19" s="28" t="str">
-        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
-        <v/>
-      </c>
-      <c r="E19" s="29">
-        <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
+      <c r="D19" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E19" s="21">
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
     </row>
@@ -8493,12 +8490,12 @@
       <c r="C20" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="D20" s="28">
-        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
+      <c r="D20" s="20">
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="E20" s="29" t="str">
-        <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
+      <c r="E20" s="21" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -8512,12 +8509,12 @@
       <c r="C21" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D21" s="28" t="str">
-        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
-        <v/>
-      </c>
-      <c r="E21" s="29">
-        <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
+      <c r="D21" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E21" s="21">
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
     </row>
@@ -8531,12 +8528,12 @@
       <c r="C22" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D22" s="28">
-        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
+      <c r="D22" s="20">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="E22" s="29" t="str">
-        <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
+      <c r="E22" s="21" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -8550,12 +8547,12 @@
       <c r="C23" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D23" s="28" t="str">
-        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
-        <v/>
-      </c>
-      <c r="E23" s="29">
-        <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
+      <c r="D23" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E23" s="21">
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
     </row>
@@ -8569,12 +8566,12 @@
       <c r="C24" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D24" s="28">
-        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
+      <c r="D24" s="20">
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="E24" s="29" t="str">
-        <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
+      <c r="E24" s="21" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -8588,12 +8585,12 @@
       <c r="C25" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D25" s="28" t="str">
-        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
-        <v/>
-      </c>
-      <c r="E25" s="29">
-        <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
+      <c r="D25" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E25" s="21">
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
     </row>
@@ -8607,12 +8604,12 @@
       <c r="C26" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D26" s="28">
-        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
+      <c r="D26" s="20">
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="E26" s="29" t="str">
-        <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
+      <c r="E26" s="21" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -8626,12 +8623,12 @@
       <c r="C27" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="D27" s="28" t="str">
-        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
-        <v/>
-      </c>
-      <c r="E27" s="29">
-        <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
+      <c r="D27" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E27" s="21">
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
     </row>
@@ -8645,12 +8642,12 @@
       <c r="C28" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D28" s="28">
-        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
+      <c r="D28" s="20">
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="E28" s="29" t="str">
-        <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
+      <c r="E28" s="21" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -8664,12 +8661,12 @@
       <c r="C29" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="D29" s="28" t="str">
-        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
-        <v/>
-      </c>
-      <c r="E29" s="29">
-        <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
+      <c r="D29" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E29" s="21">
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
     </row>
@@ -8683,12 +8680,12 @@
       <c r="C30" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D30" s="28">
-        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
+      <c r="D30" s="20">
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="E30" s="29" t="str">
-        <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
+      <c r="E30" s="21" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -8702,12 +8699,12 @@
       <c r="C31" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D31" s="28" t="str">
-        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
-        <v/>
-      </c>
-      <c r="E31" s="29">
-        <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
+      <c r="D31" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E31" s="21">
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
     </row>
@@ -8721,12 +8718,12 @@
       <c r="C32" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D32" s="28">
-        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
+      <c r="D32" s="20">
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="E32" s="29" t="str">
-        <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
+      <c r="E32" s="21" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -8740,12 +8737,12 @@
       <c r="C33" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D33" s="28" t="str">
-        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
-        <v/>
-      </c>
-      <c r="E33" s="29">
-        <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
+      <c r="D33" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E33" s="21">
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
     </row>
@@ -8753,18 +8750,18 @@
       <c r="A34" s="18">
         <v>27</v>
       </c>
-      <c r="B34" s="30" t="s">
+      <c r="B34" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="C34" s="32" t="s">
+      <c r="C34" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="D34" s="28">
-        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
+      <c r="D34" s="20">
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="E34" s="29" t="str">
-        <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
+      <c r="E34" s="21" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -8778,12 +8775,12 @@
       <c r="C35" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="D35" s="28" t="str">
-        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
-        <v/>
-      </c>
-      <c r="E35" s="29">
-        <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
+      <c r="D35" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E35" s="21">
+        <f t="shared" si="1"/>
         <v>28</v>
       </c>
     </row>
@@ -8797,12 +8794,12 @@
       <c r="C36" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D36" s="28">
-        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
+      <c r="D36" s="20">
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="E36" s="29" t="str">
-        <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
+      <c r="E36" s="21" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -8816,12 +8813,12 @@
       <c r="C37" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D37" s="28" t="str">
-        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
-        <v/>
-      </c>
-      <c r="E37" s="29">
-        <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
+      <c r="D37" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E37" s="21">
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
     </row>
@@ -8835,12 +8832,12 @@
       <c r="C38" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D38" s="28">
-        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
+      <c r="D38" s="20">
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="E38" s="29" t="str">
-        <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
+      <c r="E38" s="21" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -8854,12 +8851,12 @@
       <c r="C39" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D39" s="28" t="str">
-        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
-        <v/>
-      </c>
-      <c r="E39" s="29">
-        <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
+      <c r="D39" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E39" s="21">
+        <f t="shared" si="1"/>
         <v>32</v>
       </c>
     </row>
@@ -8873,12 +8870,12 @@
       <c r="C40" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D40" s="28">
-        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
+      <c r="D40" s="20">
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="E40" s="29" t="str">
-        <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
+      <c r="E40" s="21" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -8892,12 +8889,12 @@
       <c r="C41" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D41" s="28" t="str">
-        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
-        <v/>
-      </c>
-      <c r="E41" s="29">
-        <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
+      <c r="D41" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E41" s="21">
+        <f t="shared" si="1"/>
         <v>34</v>
       </c>
     </row>
@@ -8911,12 +8908,12 @@
       <c r="C42" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="D42" s="28">
-        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
+      <c r="D42" s="20">
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="E42" s="29" t="str">
-        <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
+      <c r="E42" s="21" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -8930,12 +8927,12 @@
       <c r="C43" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="D43" s="28" t="str">
-        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
-        <v/>
-      </c>
-      <c r="E43" s="29">
-        <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
+      <c r="D43" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E43" s="21">
+        <f t="shared" si="1"/>
         <v>36</v>
       </c>
     </row>
@@ -8949,12 +8946,12 @@
       <c r="C44" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D44" s="28">
-        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
+      <c r="D44" s="20">
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="E44" s="29" t="str">
-        <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
+      <c r="E44" s="21" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -8968,12 +8965,12 @@
       <c r="C45" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="D45" s="28" t="str">
-        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
-        <v/>
-      </c>
-      <c r="E45" s="29">
-        <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
+      <c r="D45" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E45" s="21">
+        <f t="shared" si="1"/>
         <v>38</v>
       </c>
     </row>
@@ -8987,12 +8984,12 @@
       <c r="C46" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="D46" s="28">
-        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
+      <c r="D46" s="20">
+        <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="E46" s="29" t="str">
-        <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
+      <c r="E46" s="21" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9006,12 +9003,12 @@
       <c r="C47" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D47" s="28" t="str">
-        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
-        <v/>
-      </c>
-      <c r="E47" s="29">
-        <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
+      <c r="D47" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E47" s="21">
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
     </row>
@@ -9025,12 +9022,12 @@
       <c r="C48" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="28">
-        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
-        <v>41</v>
-      </c>
-      <c r="E48" s="29" t="str">
-        <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
+      <c r="D48" s="20">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="E48" s="21" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9044,12 +9041,12 @@
       <c r="C49" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D49" s="28" t="str">
-        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
-        <v/>
-      </c>
-      <c r="E49" s="29">
-        <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
+      <c r="D49" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E49" s="21">
+        <f t="shared" si="1"/>
         <v>42</v>
       </c>
     </row>
@@ -9063,12 +9060,12 @@
       <c r="C50" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D50" s="28">
-        <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
+      <c r="D50" s="20">
+        <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="E50" s="29" t="str">
-        <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
+      <c r="E50" s="21" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -9082,8 +9079,8 @@
       <c r="C51" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D51" s="28"/>
-      <c r="E51" s="29">
+      <c r="D51" s="20"/>
+      <c r="E51" s="21">
         <v>44</v>
       </c>
     </row>
@@ -9097,11 +9094,11 @@
       <c r="C52" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D52" s="28">
+      <c r="D52" s="20">
         <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
         <v>45</v>
       </c>
-      <c r="E52" s="29" t="str">
+      <c r="E52" s="21" t="str">
         <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
         <v/>
       </c>
@@ -9116,8 +9113,8 @@
       <c r="C53" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D53" s="28"/>
-      <c r="E53" s="29">
+      <c r="D53" s="20"/>
+      <c r="E53" s="21">
         <v>46</v>
       </c>
     </row>
@@ -9131,13 +9128,13 @@
       <c r="C54" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D54" s="28">
+      <c r="D54" s="20">
         <v>47</v>
       </c>
-      <c r="E54" s="29"/>
+      <c r="E54" s="21"/>
     </row>
     <row r="55" spans="1:5" ht="13.5">
-      <c r="A55" s="20">
+      <c r="A55" s="19">
         <v>48</v>
       </c>
       <c r="B55" s="9" t="s">
@@ -9146,13 +9143,13 @@
       <c r="C55" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D55" s="28"/>
-      <c r="E55" s="29">
+      <c r="D55" s="20"/>
+      <c r="E55" s="21">
         <v>48</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="13.5">
-      <c r="A56" s="20">
+      <c r="A56" s="19">
         <v>49</v>
       </c>
       <c r="B56" s="9" t="s">
@@ -9161,13 +9158,13 @@
       <c r="C56" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="D56" s="28">
+      <c r="D56" s="20">
         <v>49</v>
       </c>
-      <c r="E56" s="29"/>
+      <c r="E56" s="21"/>
     </row>
     <row r="57" spans="1:5" ht="13.5">
-      <c r="A57" s="20">
+      <c r="A57" s="19">
         <v>50</v>
       </c>
       <c r="B57" s="9" t="s">
@@ -9176,8 +9173,8 @@
       <c r="C57" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D57" s="28"/>
-      <c r="E57" s="29">
+      <c r="D57" s="20"/>
+      <c r="E57" s="21">
         <v>50</v>
       </c>
     </row>
@@ -9191,11 +9188,11 @@
       <c r="C58" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D58" s="28">
+      <c r="D58" s="20">
         <f>IF(ISEVEN(ROW()-7),"",ROW()-7)</f>
         <v>51</v>
       </c>
-      <c r="E58" s="29" t="str">
+      <c r="E58" s="21" t="str">
         <f>IF(ISODD(ROW()-7),"",ROW()-7)</f>
         <v/>
       </c>
@@ -9210,8 +9207,8 @@
       <c r="C59" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D59" s="31"/>
-      <c r="E59" s="31">
+      <c r="D59" s="23"/>
+      <c r="E59" s="23">
         <v>52</v>
       </c>
     </row>
@@ -9225,10 +9222,10 @@
       <c r="C60" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D60" s="31">
+      <c r="D60" s="23">
         <v>53</v>
       </c>
-      <c r="E60" s="31"/>
+      <c r="E60" s="23"/>
     </row>
     <row r="61" spans="1:5">
       <c r="C61" s="2"/>
@@ -9237,10 +9234,10 @@
       <c r="B62" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="D62" s="26" t="s">
+      <c r="D62" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="E62" s="26"/>
+      <c r="E62" s="30"/>
     </row>
     <row r="63" spans="1:5" ht="15.5">
       <c r="B63" s="15" t="s">
